--- a/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
+++ b/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fstvn01\Data\10_Production Engineering Department(製造技術部)\02.製造技術課\PE Dept\20. OTHERS-その他\FILE cần lưu\PA\Tổng hợp\MP2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sandbox\MP2027\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA45185E-E29C-407C-A1F3-A78DC31D4AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5B7768-A5C0-47B9-B0F2-0AC343B9B361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3650" yWindow="10690" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配賦額一覧" sheetId="1" state="hidden" r:id="rId1"/>
@@ -39,9 +39,9 @@
     <definedName name="NO.2_Factory_" localSheetId="1">[3]SALＡRY!#REF!</definedName>
     <definedName name="NO.2_Factory_" localSheetId="0">[3]SALＡRY!#REF!</definedName>
     <definedName name="NO.2_Factory_">[3]SALＡRY!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">FY2027配賦額一覧!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">FY2027配賦額一覧!$B$4:$J$71</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">配賦額一覧!$A$1:$J$81</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">FY2027配賦額一覧!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="216">
   <si>
     <t>配布元
 Phòng phân bổ</t>
@@ -1335,6 +1335,11 @@
       </rPr>
       <t>(Bao gồm cả nhân viên biệt phái)</t>
     </r>
+  </si>
+  <si>
+    <t>入社月
+入社月の翌月
+11月</t>
   </si>
 </sst>
 </file>
@@ -5072,37 +5077,37 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="26" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1804">
@@ -5131,6 +5136,7 @@
     <cellStyle name="Accent5 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="Accent6 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="Bad 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
     <cellStyle name="Calculation 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Calculation 2 10" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="Calculation 2 11" xfId="806" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
@@ -5420,7 +5426,6 @@
     <cellStyle name="Calculation 2 8" xfId="416" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
     <cellStyle name="Calculation 2 9" xfId="451" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
     <cellStyle name="Check Cell 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Comma [0] 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
     <cellStyle name="Comma [0] 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
     <cellStyle name="Comma 10" xfId="32" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
@@ -5434,13 +5439,13 @@
     <cellStyle name="Comma 7" xfId="40" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
     <cellStyle name="Comma 8" xfId="41" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
     <cellStyle name="Comma 9" xfId="42" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Dấu phẩy [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Explanatory Text 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
     <cellStyle name="Good 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
     <cellStyle name="Heading 1 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
     <cellStyle name="Heading 2 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
     <cellStyle name="Heading 3 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
     <cellStyle name="Heading 4 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Hyperlink" xfId="92" builtinId="8"/>
     <cellStyle name="Input 2" xfId="49" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
     <cellStyle name="Input 2 10" xfId="1020" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
     <cellStyle name="Input 2 11" xfId="1171" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
@@ -5731,7 +5736,6 @@
     <cellStyle name="Input 2 9" xfId="432" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
     <cellStyle name="Linked Cell 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
     <cellStyle name="Neutral 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="52" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
     <cellStyle name="Normal 10" xfId="53" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
     <cellStyle name="Normal 11" xfId="54" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
@@ -6425,6 +6429,7 @@
     <cellStyle name="Output 2 9" xfId="410" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
     <cellStyle name="Percent 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
     <cellStyle name="Percent 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
+    <cellStyle name="Siêu kết nối" xfId="92" builtinId="8"/>
     <cellStyle name="Title 2" xfId="73" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
     <cellStyle name="Total 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
     <cellStyle name="Total 2 10" xfId="889" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
@@ -7326,22 +7331,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26.36328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="6" width="15.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
+    <col min="5" max="6" width="15.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="110" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>148</v>
       </c>
@@ -7394,8 +7399,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45.65" customHeight="1">
-      <c r="A5" s="92" t="s">
+    <row r="5" spans="1:10" ht="45.6" customHeight="1">
+      <c r="A5" s="90" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -7521,19 +7526,19 @@
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="96">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="96">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="93">
+      <c r="F9" s="96">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="93" t="s">
+      <c r="G9" s="96" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -7549,11 +7554,11 @@
     <row r="10" spans="1:10" ht="31.5" customHeight="1">
       <c r="A10" s="89"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -7625,7 +7630,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="33" customHeight="1">
-      <c r="A13" s="96"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -7745,7 +7750,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A17" s="97"/>
+      <c r="A17" s="100"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -7775,7 +7780,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="36.75" customHeight="1">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="90" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -7802,7 +7807,7 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="90" t="s">
+      <c r="J18" s="97" t="s">
         <v>176</v>
       </c>
       <c r="K18" s="10"/>
@@ -7833,7 +7838,7 @@
       <c r="I19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="91"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="10" t="s">
         <v>187</v>
       </c>
@@ -7864,7 +7869,7 @@
       <c r="I20" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="91"/>
+      <c r="J20" s="98"/>
       <c r="K20" s="10"/>
     </row>
     <row r="21" spans="1:11" ht="85.5" customHeight="1">
@@ -9064,7 +9069,7 @@
       </c>
       <c r="K60" s="57"/>
     </row>
-    <row r="61" spans="1:11" ht="92.15" customHeight="1">
+    <row r="61" spans="1:11" ht="92.1" customHeight="1">
       <c r="A61" s="89"/>
       <c r="B61" s="42" t="s">
         <v>110</v>
@@ -9219,7 +9224,7 @@
       </c>
       <c r="K65" s="10"/>
     </row>
-    <row r="66" spans="1:11" ht="138.65" customHeight="1">
+    <row r="66" spans="1:11" ht="138.6" customHeight="1">
       <c r="A66" s="89"/>
       <c r="B66" s="42" t="s">
         <v>117</v>
@@ -9250,7 +9255,7 @@
       </c>
       <c r="K66" s="10"/>
     </row>
-    <row r="67" spans="1:11" ht="314.14999999999998" customHeight="1">
+    <row r="67" spans="1:11" ht="314.10000000000002" customHeight="1">
       <c r="A67" s="89"/>
       <c r="B67" s="42" t="s">
         <v>119</v>
@@ -9693,22 +9698,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="113.36328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="113.42578125" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>189</v>
       </c>
@@ -9761,8 +9766,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.450000000000003" customHeight="1">
+      <c r="A5" s="91" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -9794,7 +9799,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A6" s="99"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="26" t="s">
         <v>16</v>
       </c>
@@ -9824,7 +9829,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A7" s="99"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="26" t="s">
         <v>18</v>
       </c>
@@ -9854,7 +9859,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A8" s="99"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="30" t="s">
         <v>21</v>
       </c>
@@ -9884,23 +9889,23 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A9" s="99"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="96">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="96">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="93">
+      <c r="F9" s="96">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="93" t="s">
+      <c r="G9" s="96" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -9914,13 +9919,13 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A10" s="99"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -9932,7 +9937,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A11" s="99"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="26" t="s">
         <v>149</v>
       </c>
@@ -9962,7 +9967,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A12" s="99"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="26" t="s">
         <v>150</v>
       </c>
@@ -9992,7 +9997,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A13" s="99"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -10022,7 +10027,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="58" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A14" s="99"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
@@ -10052,7 +10057,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A15" s="99"/>
+      <c r="A15" s="92"/>
       <c r="B15" s="42" t="s">
         <v>35</v>
       </c>
@@ -10082,7 +10087,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="58" customFormat="1" ht="84" customHeight="1">
-      <c r="A16" s="99"/>
+      <c r="A16" s="92"/>
       <c r="B16" s="42" t="s">
         <v>39</v>
       </c>
@@ -10112,7 +10117,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A17" s="100"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -10142,7 +10147,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A18" s="98" t="s">
+      <c r="A18" s="91" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -10169,12 +10174,12 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="92" t="s">
+      <c r="J18" s="90" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A19" s="99"/>
+      <c r="A19" s="92"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
@@ -10202,7 +10207,7 @@
       <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A20" s="99"/>
+      <c r="A20" s="92"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
       </c>
@@ -10230,7 +10235,7 @@
       <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A21" s="99"/>
+      <c r="A21" s="92"/>
       <c r="B21" s="26" t="s">
         <v>53</v>
       </c>
@@ -10258,7 +10263,7 @@
       <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A22" s="99"/>
+      <c r="A22" s="92"/>
       <c r="B22" s="26" t="s">
         <v>55</v>
       </c>
@@ -10288,7 +10293,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A23" s="99"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="26" t="s">
         <v>60</v>
       </c>
@@ -10318,7 +10323,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A24" s="99"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="26" t="s">
         <v>195</v>
       </c>
@@ -10346,7 +10351,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A25" s="99"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="26" t="s">
         <v>63</v>
       </c>
@@ -10374,7 +10379,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A26" s="99"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="42" t="s">
         <v>197</v>
       </c>
@@ -10402,7 +10407,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A27" s="99"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="30" t="s">
         <v>66</v>
       </c>
@@ -10430,7 +10435,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A28" s="99"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="30" t="s">
         <v>68</v>
       </c>
@@ -10458,7 +10463,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A29" s="99"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="26" t="s">
         <v>69</v>
       </c>
@@ -10488,7 +10493,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A30" s="99"/>
+      <c r="A30" s="92"/>
       <c r="B30" s="26" t="s">
         <v>72</v>
       </c>
@@ -10516,7 +10521,7 @@
       <c r="J30" s="89"/>
     </row>
     <row r="31" spans="1:10" s="58" customFormat="1" ht="66" customHeight="1">
-      <c r="A31" s="99"/>
+      <c r="A31" s="92"/>
       <c r="B31" s="42" t="s">
         <v>73</v>
       </c>
@@ -10533,7 +10538,7 @@
         <v>6005146541</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="H31" s="59">
         <v>760</v>
@@ -10546,7 +10551,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="43.5" customHeight="1">
-      <c r="A32" s="99"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="26" t="s">
         <v>74</v>
       </c>
@@ -10576,7 +10581,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A33" s="99"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="26" t="s">
         <v>77</v>
       </c>
@@ -10606,7 +10611,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A34" s="99"/>
+      <c r="A34" s="92"/>
       <c r="B34" s="26" t="s">
         <v>79</v>
       </c>
@@ -10636,7 +10641,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A35" s="99"/>
+      <c r="A35" s="92"/>
       <c r="B35" s="26" t="s">
         <v>80</v>
       </c>
@@ -10666,7 +10671,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A36" s="99"/>
+      <c r="A36" s="92"/>
       <c r="B36" s="26" t="s">
         <v>153</v>
       </c>
@@ -10696,7 +10701,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A37" s="99"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="26" t="s">
         <v>82</v>
       </c>
@@ -10726,7 +10731,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A38" s="99"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="26" t="s">
         <v>83</v>
       </c>
@@ -10756,7 +10761,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A39" s="99"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="26" t="s">
         <v>84</v>
       </c>
@@ -10786,7 +10791,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A40" s="99"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="26" t="s">
         <v>163</v>
       </c>
@@ -10816,7 +10821,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A41" s="99"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="26" t="s">
         <v>85</v>
       </c>
@@ -10846,7 +10851,7 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A42" s="99"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="26" t="s">
         <v>86</v>
       </c>
@@ -10876,7 +10881,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A43" s="99"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="26" t="s">
         <v>88</v>
       </c>
@@ -10906,7 +10911,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A44" s="99"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="26" t="s">
         <v>90</v>
       </c>
@@ -10936,7 +10941,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A45" s="99"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="42" t="s">
         <v>168</v>
       </c>
@@ -10966,7 +10971,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1">
-      <c r="A46" s="99"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="26" t="s">
         <v>173</v>
       </c>
@@ -10996,7 +11001,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A47" s="99"/>
+      <c r="A47" s="92"/>
       <c r="B47" s="42" t="s">
         <v>174</v>
       </c>
@@ -11026,7 +11031,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1">
-      <c r="A48" s="99"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="26" t="s">
         <v>91</v>
       </c>
@@ -11056,7 +11061,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1">
-      <c r="A49" s="99"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="26" t="s">
         <v>92</v>
       </c>
@@ -11086,7 +11091,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1">
-      <c r="A50" s="99"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="26" t="s">
         <v>94</v>
       </c>
@@ -11116,7 +11121,7 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A51" s="99"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="26" t="s">
         <v>95</v>
       </c>
@@ -11146,7 +11151,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A52" s="99"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="26" t="s">
         <v>96</v>
       </c>
@@ -11176,7 +11181,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A53" s="99"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="26" t="s">
         <v>97</v>
       </c>
@@ -11206,7 +11211,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A54" s="99"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="26" t="s">
         <v>99</v>
       </c>
@@ -11236,7 +11241,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="58" customFormat="1" ht="85.5" customHeight="1">
-      <c r="A55" s="99"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="42" t="s">
         <v>101</v>
       </c>
@@ -11266,7 +11271,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A56" s="99"/>
+      <c r="A56" s="92"/>
       <c r="B56" s="42" t="s">
         <v>102</v>
       </c>
@@ -11296,7 +11301,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A57" s="99"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="42" t="s">
         <v>104</v>
       </c>
@@ -11326,7 +11331,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A58" s="99"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="42" t="s">
         <v>105</v>
       </c>
@@ -11356,7 +11361,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" s="65" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A59" s="99"/>
+      <c r="A59" s="92"/>
       <c r="B59" s="56" t="s">
         <v>106</v>
       </c>
@@ -11386,7 +11391,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="71" customFormat="1" ht="60" customHeight="1">
-      <c r="A60" s="99"/>
+      <c r="A60" s="92"/>
       <c r="B60" s="42" t="s">
         <v>210</v>
       </c>
@@ -11416,7 +11421,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="114" customHeight="1">
-      <c r="A61" s="99"/>
+      <c r="A61" s="92"/>
       <c r="B61" s="42" t="s">
         <v>107</v>
       </c>
@@ -11446,7 +11451,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="139.15" customHeight="1">
-      <c r="A62" s="99"/>
+      <c r="A62" s="92"/>
       <c r="B62" s="42" t="s">
         <v>171</v>
       </c>
@@ -11476,7 +11481,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" s="58" customFormat="1" ht="93.75" customHeight="1">
-      <c r="A63" s="99"/>
+      <c r="A63" s="92"/>
       <c r="B63" s="42" t="s">
         <v>109</v>
       </c>
@@ -11506,7 +11511,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="135" customHeight="1">
-      <c r="A64" s="99"/>
+      <c r="A64" s="92"/>
       <c r="B64" s="42" t="s">
         <v>110</v>
       </c>
@@ -11536,7 +11541,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="138" customHeight="1">
-      <c r="A65" s="99"/>
+      <c r="A65" s="92"/>
       <c r="B65" s="41" t="s">
         <v>111</v>
       </c>
@@ -11566,7 +11571,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="96" customHeight="1">
-      <c r="A66" s="99"/>
+      <c r="A66" s="92"/>
       <c r="B66" s="41" t="s">
         <v>113</v>
       </c>
@@ -11596,7 +11601,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="95.25" customHeight="1">
-      <c r="A67" s="99"/>
+      <c r="A67" s="92"/>
       <c r="B67" s="42" t="s">
         <v>147</v>
       </c>
@@ -11626,7 +11631,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" s="65" customFormat="1" ht="60" customHeight="1">
-      <c r="A68" s="99"/>
+      <c r="A68" s="92"/>
       <c r="B68" s="56" t="s">
         <v>116</v>
       </c>
@@ -11656,7 +11661,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="163.5" customHeight="1">
-      <c r="A69" s="99"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="42" t="s">
         <v>117</v>
       </c>
@@ -11686,7 +11691,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="334.5" customHeight="1">
-      <c r="A70" s="99"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="42" t="s">
         <v>119</v>
       </c>
@@ -11716,7 +11721,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" s="71" customFormat="1" ht="150" customHeight="1">
-      <c r="A71" s="100"/>
+      <c r="A71" s="93"/>
       <c r="B71" s="80" t="s">
         <v>211</v>
       </c>
@@ -11844,17 +11849,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x010100DB24EDB465323845A68F49B67C0FBEEF" ma:contentTypeVersion="17" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="23f0dc0ab5ad78d6e6291fdb2fe26642">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3666f02-6a17-4b93-8e4f-4f8c851bed15" xmlns:ns3="a67f3886-f84f-4ade-a9df-8a61292dc710" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7e7713e468ce5fe561a860222c69c2e" ns2:_="" ns3:_="">
     <xsd:import namespace="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
@@ -12031,32 +12025,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
-    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC458EFE-CB2F-4B14-8A64-8A5C4D5C5CBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12073,4 +12053,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
+    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
+++ b/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sandbox\MP2027\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fstvn01\Data\10_Production Engineering Department(製造技術部)\02.製造技術課\PE Dept\20. OTHERS-その他\FILE cần lưu\PA\Tổng hợp\MP2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5B7768-A5C0-47B9-B0F2-0AC343B9B361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA45185E-E29C-407C-A1F3-A78DC31D4AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3650" yWindow="10690" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配賦額一覧" sheetId="1" state="hidden" r:id="rId1"/>
@@ -39,9 +39,9 @@
     <definedName name="NO.2_Factory_" localSheetId="1">[3]SALＡRY!#REF!</definedName>
     <definedName name="NO.2_Factory_" localSheetId="0">[3]SALＡRY!#REF!</definedName>
     <definedName name="NO.2_Factory_">[3]SALＡRY!#REF!</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">FY2027配賦額一覧!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">FY2027配賦額一覧!$B$4:$J$71</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">配賦額一覧!$A$1:$J$81</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">FY2027配賦額一覧!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="215">
   <si>
     <t>配布元
 Phòng phân bổ</t>
@@ -1335,11 +1335,6 @@
       </rPr>
       <t>(Bao gồm cả nhân viên biệt phái)</t>
     </r>
-  </si>
-  <si>
-    <t>入社月
-入社月の翌月
-11月</t>
   </si>
 </sst>
 </file>
@@ -5077,6 +5072,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="26" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5087,27 +5103,6 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1804">
@@ -5136,7 +5131,6 @@
     <cellStyle name="Accent5 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="Accent6 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="Bad 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
     <cellStyle name="Calculation 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Calculation 2 10" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="Calculation 2 11" xfId="806" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
@@ -5426,6 +5420,7 @@
     <cellStyle name="Calculation 2 8" xfId="416" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
     <cellStyle name="Calculation 2 9" xfId="451" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
     <cellStyle name="Check Cell 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Comma [0] 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
     <cellStyle name="Comma [0] 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
     <cellStyle name="Comma 10" xfId="32" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
@@ -5439,13 +5434,13 @@
     <cellStyle name="Comma 7" xfId="40" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
     <cellStyle name="Comma 8" xfId="41" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
     <cellStyle name="Comma 9" xfId="42" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Dấu phẩy [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Explanatory Text 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
     <cellStyle name="Good 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
     <cellStyle name="Heading 1 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
     <cellStyle name="Heading 2 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
     <cellStyle name="Heading 3 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
     <cellStyle name="Heading 4 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Hyperlink" xfId="92" builtinId="8"/>
     <cellStyle name="Input 2" xfId="49" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
     <cellStyle name="Input 2 10" xfId="1020" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
     <cellStyle name="Input 2 11" xfId="1171" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
@@ -5736,6 +5731,7 @@
     <cellStyle name="Input 2 9" xfId="432" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
     <cellStyle name="Linked Cell 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
     <cellStyle name="Neutral 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="52" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
     <cellStyle name="Normal 10" xfId="53" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
     <cellStyle name="Normal 11" xfId="54" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
@@ -6429,7 +6425,6 @@
     <cellStyle name="Output 2 9" xfId="410" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
     <cellStyle name="Percent 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
     <cellStyle name="Percent 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
-    <cellStyle name="Siêu kết nối" xfId="92" builtinId="8"/>
     <cellStyle name="Title 2" xfId="73" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
     <cellStyle name="Total 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
     <cellStyle name="Total 2 10" xfId="889" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
@@ -7331,22 +7326,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="6" width="15.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="15.26953125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.7265625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
     <col min="10" max="10" width="110" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.5">
       <c r="A1" s="1" t="s">
         <v>148</v>
       </c>
@@ -7399,8 +7394,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45.6" customHeight="1">
-      <c r="A5" s="90" t="s">
+    <row r="5" spans="1:10" ht="45.65" customHeight="1">
+      <c r="A5" s="92" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -7526,19 +7521,19 @@
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="93">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="93">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="93">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="96" t="s">
+      <c r="G9" s="93" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -7554,11 +7549,11 @@
     <row r="10" spans="1:10" ht="31.5" customHeight="1">
       <c r="A10" s="89"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -7630,7 +7625,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="33" customHeight="1">
-      <c r="A13" s="99"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -7750,7 +7745,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A17" s="100"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -7780,7 +7775,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="36.75" customHeight="1">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="92" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -7807,7 +7802,7 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="97" t="s">
+      <c r="J18" s="90" t="s">
         <v>176</v>
       </c>
       <c r="K18" s="10"/>
@@ -7838,7 +7833,7 @@
       <c r="I19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="98"/>
+      <c r="J19" s="91"/>
       <c r="K19" s="10" t="s">
         <v>187</v>
       </c>
@@ -7869,7 +7864,7 @@
       <c r="I20" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="98"/>
+      <c r="J20" s="91"/>
       <c r="K20" s="10"/>
     </row>
     <row r="21" spans="1:11" ht="85.5" customHeight="1">
@@ -9069,7 +9064,7 @@
       </c>
       <c r="K60" s="57"/>
     </row>
-    <row r="61" spans="1:11" ht="92.1" customHeight="1">
+    <row r="61" spans="1:11" ht="92.15" customHeight="1">
       <c r="A61" s="89"/>
       <c r="B61" s="42" t="s">
         <v>110</v>
@@ -9224,7 +9219,7 @@
       </c>
       <c r="K65" s="10"/>
     </row>
-    <row r="66" spans="1:11" ht="138.6" customHeight="1">
+    <row r="66" spans="1:11" ht="138.65" customHeight="1">
       <c r="A66" s="89"/>
       <c r="B66" s="42" t="s">
         <v>117</v>
@@ -9255,7 +9250,7 @@
       </c>
       <c r="K66" s="10"/>
     </row>
-    <row r="67" spans="1:11" ht="314.10000000000002" customHeight="1">
+    <row r="67" spans="1:11" ht="314.14999999999998" customHeight="1">
       <c r="A67" s="89"/>
       <c r="B67" s="42" t="s">
         <v>119</v>
@@ -9698,22 +9693,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.26953125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="113.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="113.36328125" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
+    <row r="1" spans="1:10" ht="17.5">
       <c r="A1" s="1" t="s">
         <v>189</v>
       </c>
@@ -9766,8 +9761,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.450000000000003" customHeight="1">
-      <c r="A5" s="91" t="s">
+    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.5" customHeight="1">
+      <c r="A5" s="98" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -9799,7 +9794,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A6" s="92"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="26" t="s">
         <v>16</v>
       </c>
@@ -9829,7 +9824,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A7" s="92"/>
+      <c r="A7" s="99"/>
       <c r="B7" s="26" t="s">
         <v>18</v>
       </c>
@@ -9859,7 +9854,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A8" s="92"/>
+      <c r="A8" s="99"/>
       <c r="B8" s="30" t="s">
         <v>21</v>
       </c>
@@ -9889,23 +9884,23 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A9" s="92"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="93">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="93">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="93">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="96" t="s">
+      <c r="G9" s="93" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -9919,13 +9914,13 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A10" s="92"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -9937,7 +9932,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A11" s="92"/>
+      <c r="A11" s="99"/>
       <c r="B11" s="26" t="s">
         <v>149</v>
       </c>
@@ -9967,7 +9962,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A12" s="92"/>
+      <c r="A12" s="99"/>
       <c r="B12" s="26" t="s">
         <v>150</v>
       </c>
@@ -9997,7 +9992,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A13" s="92"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -10027,7 +10022,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="58" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A14" s="92"/>
+      <c r="A14" s="99"/>
       <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
@@ -10057,7 +10052,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A15" s="92"/>
+      <c r="A15" s="99"/>
       <c r="B15" s="42" t="s">
         <v>35</v>
       </c>
@@ -10087,7 +10082,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="58" customFormat="1" ht="84" customHeight="1">
-      <c r="A16" s="92"/>
+      <c r="A16" s="99"/>
       <c r="B16" s="42" t="s">
         <v>39</v>
       </c>
@@ -10117,7 +10112,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A17" s="93"/>
+      <c r="A17" s="100"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -10147,7 +10142,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="98" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -10174,12 +10169,12 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="90" t="s">
+      <c r="J18" s="92" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A19" s="92"/>
+      <c r="A19" s="99"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
@@ -10207,7 +10202,7 @@
       <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A20" s="92"/>
+      <c r="A20" s="99"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
       </c>
@@ -10235,7 +10230,7 @@
       <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A21" s="92"/>
+      <c r="A21" s="99"/>
       <c r="B21" s="26" t="s">
         <v>53</v>
       </c>
@@ -10263,7 +10258,7 @@
       <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A22" s="92"/>
+      <c r="A22" s="99"/>
       <c r="B22" s="26" t="s">
         <v>55</v>
       </c>
@@ -10293,7 +10288,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A23" s="92"/>
+      <c r="A23" s="99"/>
       <c r="B23" s="26" t="s">
         <v>60</v>
       </c>
@@ -10323,7 +10318,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A24" s="92"/>
+      <c r="A24" s="99"/>
       <c r="B24" s="26" t="s">
         <v>195</v>
       </c>
@@ -10351,7 +10346,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A25" s="92"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="26" t="s">
         <v>63</v>
       </c>
@@ -10379,7 +10374,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A26" s="92"/>
+      <c r="A26" s="99"/>
       <c r="B26" s="42" t="s">
         <v>197</v>
       </c>
@@ -10407,7 +10402,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A27" s="92"/>
+      <c r="A27" s="99"/>
       <c r="B27" s="30" t="s">
         <v>66</v>
       </c>
@@ -10435,7 +10430,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A28" s="92"/>
+      <c r="A28" s="99"/>
       <c r="B28" s="30" t="s">
         <v>68</v>
       </c>
@@ -10463,7 +10458,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A29" s="92"/>
+      <c r="A29" s="99"/>
       <c r="B29" s="26" t="s">
         <v>69</v>
       </c>
@@ -10493,7 +10488,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A30" s="92"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="26" t="s">
         <v>72</v>
       </c>
@@ -10521,7 +10516,7 @@
       <c r="J30" s="89"/>
     </row>
     <row r="31" spans="1:10" s="58" customFormat="1" ht="66" customHeight="1">
-      <c r="A31" s="92"/>
+      <c r="A31" s="99"/>
       <c r="B31" s="42" t="s">
         <v>73</v>
       </c>
@@ -10538,7 +10533,7 @@
         <v>6005146541</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="H31" s="59">
         <v>760</v>
@@ -10551,7 +10546,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="43.5" customHeight="1">
-      <c r="A32" s="92"/>
+      <c r="A32" s="99"/>
       <c r="B32" s="26" t="s">
         <v>74</v>
       </c>
@@ -10581,7 +10576,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A33" s="92"/>
+      <c r="A33" s="99"/>
       <c r="B33" s="26" t="s">
         <v>77</v>
       </c>
@@ -10611,7 +10606,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A34" s="92"/>
+      <c r="A34" s="99"/>
       <c r="B34" s="26" t="s">
         <v>79</v>
       </c>
@@ -10641,7 +10636,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A35" s="92"/>
+      <c r="A35" s="99"/>
       <c r="B35" s="26" t="s">
         <v>80</v>
       </c>
@@ -10671,7 +10666,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A36" s="92"/>
+      <c r="A36" s="99"/>
       <c r="B36" s="26" t="s">
         <v>153</v>
       </c>
@@ -10701,7 +10696,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A37" s="92"/>
+      <c r="A37" s="99"/>
       <c r="B37" s="26" t="s">
         <v>82</v>
       </c>
@@ -10731,7 +10726,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A38" s="92"/>
+      <c r="A38" s="99"/>
       <c r="B38" s="26" t="s">
         <v>83</v>
       </c>
@@ -10761,7 +10756,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A39" s="92"/>
+      <c r="A39" s="99"/>
       <c r="B39" s="26" t="s">
         <v>84</v>
       </c>
@@ -10791,7 +10786,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A40" s="92"/>
+      <c r="A40" s="99"/>
       <c r="B40" s="26" t="s">
         <v>163</v>
       </c>
@@ -10821,7 +10816,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A41" s="92"/>
+      <c r="A41" s="99"/>
       <c r="B41" s="26" t="s">
         <v>85</v>
       </c>
@@ -10851,7 +10846,7 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A42" s="92"/>
+      <c r="A42" s="99"/>
       <c r="B42" s="26" t="s">
         <v>86</v>
       </c>
@@ -10881,7 +10876,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A43" s="92"/>
+      <c r="A43" s="99"/>
       <c r="B43" s="26" t="s">
         <v>88</v>
       </c>
@@ -10911,7 +10906,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A44" s="92"/>
+      <c r="A44" s="99"/>
       <c r="B44" s="26" t="s">
         <v>90</v>
       </c>
@@ -10941,7 +10936,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A45" s="92"/>
+      <c r="A45" s="99"/>
       <c r="B45" s="42" t="s">
         <v>168</v>
       </c>
@@ -10971,7 +10966,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1">
-      <c r="A46" s="92"/>
+      <c r="A46" s="99"/>
       <c r="B46" s="26" t="s">
         <v>173</v>
       </c>
@@ -11001,7 +10996,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A47" s="92"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="42" t="s">
         <v>174</v>
       </c>
@@ -11031,7 +11026,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1">
-      <c r="A48" s="92"/>
+      <c r="A48" s="99"/>
       <c r="B48" s="26" t="s">
         <v>91</v>
       </c>
@@ -11061,7 +11056,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1">
-      <c r="A49" s="92"/>
+      <c r="A49" s="99"/>
       <c r="B49" s="26" t="s">
         <v>92</v>
       </c>
@@ -11091,7 +11086,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1">
-      <c r="A50" s="92"/>
+      <c r="A50" s="99"/>
       <c r="B50" s="26" t="s">
         <v>94</v>
       </c>
@@ -11121,7 +11116,7 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A51" s="92"/>
+      <c r="A51" s="99"/>
       <c r="B51" s="26" t="s">
         <v>95</v>
       </c>
@@ -11151,7 +11146,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A52" s="92"/>
+      <c r="A52" s="99"/>
       <c r="B52" s="26" t="s">
         <v>96</v>
       </c>
@@ -11181,7 +11176,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A53" s="92"/>
+      <c r="A53" s="99"/>
       <c r="B53" s="26" t="s">
         <v>97</v>
       </c>
@@ -11211,7 +11206,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A54" s="92"/>
+      <c r="A54" s="99"/>
       <c r="B54" s="26" t="s">
         <v>99</v>
       </c>
@@ -11241,7 +11236,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="58" customFormat="1" ht="85.5" customHeight="1">
-      <c r="A55" s="92"/>
+      <c r="A55" s="99"/>
       <c r="B55" s="42" t="s">
         <v>101</v>
       </c>
@@ -11271,7 +11266,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A56" s="92"/>
+      <c r="A56" s="99"/>
       <c r="B56" s="42" t="s">
         <v>102</v>
       </c>
@@ -11301,7 +11296,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A57" s="92"/>
+      <c r="A57" s="99"/>
       <c r="B57" s="42" t="s">
         <v>104</v>
       </c>
@@ -11331,7 +11326,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A58" s="92"/>
+      <c r="A58" s="99"/>
       <c r="B58" s="42" t="s">
         <v>105</v>
       </c>
@@ -11361,7 +11356,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" s="65" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A59" s="92"/>
+      <c r="A59" s="99"/>
       <c r="B59" s="56" t="s">
         <v>106</v>
       </c>
@@ -11391,7 +11386,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="71" customFormat="1" ht="60" customHeight="1">
-      <c r="A60" s="92"/>
+      <c r="A60" s="99"/>
       <c r="B60" s="42" t="s">
         <v>210</v>
       </c>
@@ -11421,7 +11416,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="114" customHeight="1">
-      <c r="A61" s="92"/>
+      <c r="A61" s="99"/>
       <c r="B61" s="42" t="s">
         <v>107</v>
       </c>
@@ -11451,7 +11446,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="139.15" customHeight="1">
-      <c r="A62" s="92"/>
+      <c r="A62" s="99"/>
       <c r="B62" s="42" t="s">
         <v>171</v>
       </c>
@@ -11481,7 +11476,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" s="58" customFormat="1" ht="93.75" customHeight="1">
-      <c r="A63" s="92"/>
+      <c r="A63" s="99"/>
       <c r="B63" s="42" t="s">
         <v>109</v>
       </c>
@@ -11511,7 +11506,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="135" customHeight="1">
-      <c r="A64" s="92"/>
+      <c r="A64" s="99"/>
       <c r="B64" s="42" t="s">
         <v>110</v>
       </c>
@@ -11541,7 +11536,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="138" customHeight="1">
-      <c r="A65" s="92"/>
+      <c r="A65" s="99"/>
       <c r="B65" s="41" t="s">
         <v>111</v>
       </c>
@@ -11571,7 +11566,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="96" customHeight="1">
-      <c r="A66" s="92"/>
+      <c r="A66" s="99"/>
       <c r="B66" s="41" t="s">
         <v>113</v>
       </c>
@@ -11601,7 +11596,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="95.25" customHeight="1">
-      <c r="A67" s="92"/>
+      <c r="A67" s="99"/>
       <c r="B67" s="42" t="s">
         <v>147</v>
       </c>
@@ -11631,7 +11626,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" s="65" customFormat="1" ht="60" customHeight="1">
-      <c r="A68" s="92"/>
+      <c r="A68" s="99"/>
       <c r="B68" s="56" t="s">
         <v>116</v>
       </c>
@@ -11661,7 +11656,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="163.5" customHeight="1">
-      <c r="A69" s="92"/>
+      <c r="A69" s="99"/>
       <c r="B69" s="42" t="s">
         <v>117</v>
       </c>
@@ -11691,7 +11686,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="334.5" customHeight="1">
-      <c r="A70" s="92"/>
+      <c r="A70" s="99"/>
       <c r="B70" s="42" t="s">
         <v>119</v>
       </c>
@@ -11721,7 +11716,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" s="71" customFormat="1" ht="150" customHeight="1">
-      <c r="A71" s="93"/>
+      <c r="A71" s="100"/>
       <c r="B71" s="80" t="s">
         <v>211</v>
       </c>
@@ -11849,6 +11844,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x010100DB24EDB465323845A68F49B67C0FBEEF" ma:contentTypeVersion="17" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="23f0dc0ab5ad78d6e6291fdb2fe26642">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3666f02-6a17-4b93-8e4f-4f8c851bed15" xmlns:ns3="a67f3886-f84f-4ade-a9df-8a61292dc710" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7e7713e468ce5fe561a860222c69c2e" ns2:_="" ns3:_="">
     <xsd:import namespace="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
@@ -12025,18 +12031,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
+    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC458EFE-CB2F-4B14-8A64-8A5C4D5C5CBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12053,29 +12073,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
-    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
+++ b/docs/MP2027/FY2027配賦額一覧 (2025.12.29).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fstvn01\Data\10_Production Engineering Department(製造技術部)\02.製造技術課\PE Dept\20. OTHERS-その他\FILE cần lưu\PA\Tổng hợp\MP2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sandbox\MP2027\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA45185E-E29C-407C-A1F3-A78DC31D4AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FAC7A6-D537-48F9-B3E4-A5D2CE397D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配賦額一覧" sheetId="1" state="hidden" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="217">
   <si>
     <t>配布元
 Phòng phân bổ</t>
@@ -1336,22 +1336,97 @@
       <t>(Bao gồm cả nhân viên biệt phái)</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>入社月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>入社月の翌月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <phoneticPr fontId="36"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ 明朝"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ポケットカレンダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Lịch bỏ túi</t>
+    </r>
+    <phoneticPr fontId="36"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0_);[Red]\-#,##0_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="#,##0_);[Red]\-#,##0_)"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1359,56 +1434,56 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1476,7 +1551,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1581,14 +1656,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1681,6 +1756,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times"/>
       <family val="1"/>
       <charset val="128"/>
     </font>
@@ -2883,7 +2972,7 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2893,15 +2982,15 @@
     <xf numFmtId="40" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="40" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="40" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2959,9 +3048,9 @@
     <xf numFmtId="40" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2998,7 +3087,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3007,8 +3096,8 @@
     <xf numFmtId="0" fontId="31" fillId="21" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
@@ -3021,7 +3110,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3042,7 +3131,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3055,7 +3144,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3071,7 +3160,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3085,7 +3174,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3098,7 +3187,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3114,7 +3203,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3128,7 +3217,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3141,7 +3230,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3157,7 +3246,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3171,7 +3260,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3184,7 +3273,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3200,7 +3289,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3214,7 +3303,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3227,7 +3316,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3243,7 +3332,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3257,7 +3346,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3270,7 +3359,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3286,7 +3375,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3300,7 +3389,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3313,7 +3402,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3329,7 +3418,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3416,7 +3505,7 @@
     <xf numFmtId="0" fontId="13" fillId="21" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="47" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="55" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -3439,7 +3528,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3459,7 +3548,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3475,7 +3564,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3488,7 +3577,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3504,7 +3593,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3518,7 +3607,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3531,7 +3620,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3547,7 +3636,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3561,7 +3650,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3574,7 +3663,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3590,7 +3679,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3604,7 +3693,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3617,7 +3706,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3633,7 +3722,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3647,7 +3736,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3660,7 +3749,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3676,7 +3765,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3690,7 +3779,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3703,7 +3792,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3719,7 +3808,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3733,7 +3822,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3746,7 +3835,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3762,7 +3851,7 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -4802,7 +4891,7 @@
     <xf numFmtId="0" fontId="31" fillId="21" borderId="67" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4849,7 +4938,7 @@
     <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="92" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5072,37 +5161,43 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="70" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="26" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1804">
@@ -7326,22 +7421,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26.36328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="6" width="15.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
+    <col min="5" max="6" width="15.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="110" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>148</v>
       </c>
@@ -7349,20 +7444,20 @@
       <c r="F1" s="4"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="C2" s="3"/>
       <c r="F2" s="4"/>
       <c r="H2" s="13"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="63" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="3"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:10" ht="40.5" customHeight="1">
+    <row r="4" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -7394,8 +7489,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45.65" customHeight="1">
-      <c r="A5" s="92" t="s">
+    <row r="5" spans="1:10" ht="45.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="90" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -7426,7 +7521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="31.5" customHeight="1">
+    <row r="6" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="89"/>
       <c r="B6" s="26" t="s">
         <v>16</v>
@@ -7456,7 +7551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="31.5" customHeight="1">
+    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="89"/>
       <c r="B7" s="26" t="s">
         <v>18</v>
@@ -7486,7 +7581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="31.5" customHeight="1">
+    <row r="8" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="89"/>
       <c r="B8" s="30" t="s">
         <v>21</v>
@@ -7516,24 +7611,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="31.5" customHeight="1">
+    <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="89"/>
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="96">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="96">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="93">
+      <c r="F9" s="96">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="93" t="s">
+      <c r="G9" s="96" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -7546,14 +7641,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="31.5" customHeight="1">
+    <row r="10" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="89"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -7564,7 +7659,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="33.75" customHeight="1">
+    <row r="11" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="89"/>
       <c r="B11" s="26" t="s">
         <v>149</v>
@@ -7594,7 +7689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="33.75" customHeight="1">
+    <row r="12" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="89"/>
       <c r="B12" s="26" t="s">
         <v>150</v>
@@ -7624,8 +7719,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="33" customHeight="1">
-      <c r="A13" s="96"/>
+    <row r="13" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="99"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -7654,7 +7749,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="88.5" customHeight="1">
+    <row r="14" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="89"/>
       <c r="B14" s="42" t="s">
         <v>32</v>
@@ -7684,7 +7779,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="34.5" customHeight="1">
+    <row r="15" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="89"/>
       <c r="B15" s="56" t="s">
         <v>35</v>
@@ -7714,7 +7809,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="79.150000000000006" customHeight="1">
+    <row r="16" spans="1:10" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="89"/>
       <c r="B16" s="56" t="s">
         <v>39</v>
@@ -7744,8 +7839,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A17" s="97"/>
+    <row r="17" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="100"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -7774,8 +7869,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="36.75" customHeight="1">
-      <c r="A18" s="92" t="s">
+    <row r="18" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="90" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -7802,12 +7897,12 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="90" t="s">
+      <c r="J18" s="97" t="s">
         <v>176</v>
       </c>
       <c r="K18" s="10"/>
     </row>
-    <row r="19" spans="1:11" ht="36.75" customHeight="1">
+    <row r="19" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="89"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
@@ -7833,12 +7928,12 @@
       <c r="I19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="91"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="10" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="36.75" customHeight="1">
+    <row r="20" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="89"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
@@ -7864,10 +7959,10 @@
       <c r="I20" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="91"/>
+      <c r="J20" s="98"/>
       <c r="K20" s="10"/>
     </row>
-    <row r="21" spans="1:11" ht="85.5" customHeight="1">
+    <row r="21" spans="1:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="89"/>
       <c r="B21" s="26" t="s">
         <v>53</v>
@@ -7898,7 +7993,7 @@
       </c>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="36.75" customHeight="1">
+    <row r="22" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="89"/>
       <c r="B22" s="26" t="s">
         <v>55</v>
@@ -7928,7 +8023,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="36.75" customHeight="1">
+    <row r="23" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="89"/>
       <c r="B23" s="26" t="s">
         <v>60</v>
@@ -7958,7 +8053,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="36.75" customHeight="1">
+    <row r="24" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="89"/>
       <c r="B24" s="26" t="s">
         <v>63</v>
@@ -7986,7 +8081,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="36.75" customHeight="1">
+    <row r="25" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="89"/>
       <c r="B25" s="30" t="s">
         <v>66</v>
@@ -8014,7 +8109,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="36.75" customHeight="1">
+    <row r="26" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="89"/>
       <c r="B26" s="30" t="s">
         <v>68</v>
@@ -8042,7 +8137,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="46.5" customHeight="1">
+    <row r="27" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="89"/>
       <c r="B27" s="26" t="s">
         <v>69</v>
@@ -8073,7 +8168,7 @@
       </c>
       <c r="K27" s="10"/>
     </row>
-    <row r="28" spans="1:11" ht="46.5" customHeight="1">
+    <row r="28" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="89"/>
       <c r="B28" s="26" t="s">
         <v>72</v>
@@ -8102,7 +8197,7 @@
       <c r="J28" s="89"/>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" spans="1:11" s="58" customFormat="1" ht="66" customHeight="1">
+    <row r="29" spans="1:11" s="58" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="89"/>
       <c r="B29" s="42" t="s">
         <v>73</v>
@@ -8133,7 +8228,7 @@
       </c>
       <c r="K29" s="57"/>
     </row>
-    <row r="30" spans="1:11" ht="43.5" customHeight="1">
+    <row r="30" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="89"/>
       <c r="B30" s="26" t="s">
         <v>74</v>
@@ -8163,7 +8258,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="93" customHeight="1">
+    <row r="31" spans="1:11" ht="93" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="89"/>
       <c r="B31" s="26" t="s">
         <v>77</v>
@@ -8193,7 +8288,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="39.75" customHeight="1">
+    <row r="32" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="89"/>
       <c r="B32" s="26" t="s">
         <v>79</v>
@@ -8223,7 +8318,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="39.75" customHeight="1">
+    <row r="33" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="89"/>
       <c r="B33" s="26" t="s">
         <v>80</v>
@@ -8253,7 +8348,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="39.75" customHeight="1">
+    <row r="34" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="89"/>
       <c r="B34" s="26" t="s">
         <v>153</v>
@@ -8283,7 +8378,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="39.75" customHeight="1">
+    <row r="35" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="89"/>
       <c r="B35" s="26" t="s">
         <v>82</v>
@@ -8313,7 +8408,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="39.75" customHeight="1">
+    <row r="36" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="89"/>
       <c r="B36" s="26" t="s">
         <v>83</v>
@@ -8343,7 +8438,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="39.75" customHeight="1">
+    <row r="37" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="89"/>
       <c r="B37" s="26" t="s">
         <v>84</v>
@@ -8373,7 +8468,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="39.75" customHeight="1">
+    <row r="38" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="89"/>
       <c r="B38" s="26" t="s">
         <v>163</v>
@@ -8403,7 +8498,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="39.75" customHeight="1">
+    <row r="39" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="89"/>
       <c r="B39" s="26" t="s">
         <v>85</v>
@@ -8433,7 +8528,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="39.75" customHeight="1">
+    <row r="40" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="89"/>
       <c r="B40" s="26" t="s">
         <v>86</v>
@@ -8463,7 +8558,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="39.75" customHeight="1">
+    <row r="41" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="89"/>
       <c r="B41" s="26" t="s">
         <v>88</v>
@@ -8493,7 +8588,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="39.75" customHeight="1">
+    <row r="42" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="89"/>
       <c r="B42" s="26" t="s">
         <v>90</v>
@@ -8523,7 +8618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="39.75" customHeight="1">
+    <row r="43" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="89"/>
       <c r="B43" s="42" t="s">
         <v>168</v>
@@ -8553,7 +8648,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="42" customHeight="1">
+    <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="89"/>
       <c r="B44" s="26" t="s">
         <v>173</v>
@@ -8583,7 +8678,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="99.75" customHeight="1">
+    <row r="45" spans="1:10" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="89"/>
       <c r="B45" s="42" t="s">
         <v>174</v>
@@ -8613,7 +8708,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="42" customHeight="1">
+    <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="89"/>
       <c r="B46" s="26" t="s">
         <v>91</v>
@@ -8643,7 +8738,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="42" customHeight="1">
+    <row r="47" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="89"/>
       <c r="B47" s="26" t="s">
         <v>92</v>
@@ -8673,7 +8768,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="42" customHeight="1">
+    <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="89"/>
       <c r="B48" s="26" t="s">
         <v>94</v>
@@ -8703,7 +8798,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42.75" customHeight="1">
+    <row r="49" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="89"/>
       <c r="B49" s="26" t="s">
         <v>95</v>
@@ -8733,7 +8828,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42.75" customHeight="1">
+    <row r="50" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="89"/>
       <c r="B50" s="26" t="s">
         <v>96</v>
@@ -8763,7 +8858,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42.75" customHeight="1">
+    <row r="51" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="89"/>
       <c r="B51" s="26" t="s">
         <v>97</v>
@@ -8793,7 +8888,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42.75" customHeight="1">
+    <row r="52" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="89"/>
       <c r="B52" s="26" t="s">
         <v>99</v>
@@ -8823,7 +8918,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="65" customFormat="1" ht="85.5" customHeight="1">
+    <row r="53" spans="1:11" s="65" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="89"/>
       <c r="B53" s="56" t="s">
         <v>101</v>
@@ -8853,7 +8948,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="34.5" customHeight="1">
+    <row r="54" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="89"/>
       <c r="B54" s="42" t="s">
         <v>102</v>
@@ -8883,7 +8978,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="34.5" customHeight="1">
+    <row r="55" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="89"/>
       <c r="B55" s="42" t="s">
         <v>104</v>
@@ -8913,7 +9008,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="34.5" customHeight="1">
+    <row r="56" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="89"/>
       <c r="B56" s="42" t="s">
         <v>105</v>
@@ -8943,7 +9038,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="54.75" customHeight="1">
+    <row r="57" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="89"/>
       <c r="B57" s="42" t="s">
         <v>106</v>
@@ -8973,7 +9068,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="114" customHeight="1">
+    <row r="58" spans="1:11" ht="114" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="89"/>
       <c r="B58" s="42" t="s">
         <v>107</v>
@@ -9003,7 +9098,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="139.15" customHeight="1">
+    <row r="59" spans="1:11" ht="139.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="89"/>
       <c r="B59" s="42" t="s">
         <v>171</v>
@@ -9033,7 +9128,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="58" customFormat="1" ht="93.75" customHeight="1">
+    <row r="60" spans="1:11" s="58" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="89"/>
       <c r="B60" s="42" t="s">
         <v>109</v>
@@ -9064,7 +9159,7 @@
       </c>
       <c r="K60" s="57"/>
     </row>
-    <row r="61" spans="1:11" ht="92.15" customHeight="1">
+    <row r="61" spans="1:11" ht="92.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="89"/>
       <c r="B61" s="42" t="s">
         <v>110</v>
@@ -9095,7 +9190,7 @@
       </c>
       <c r="K61" s="10"/>
     </row>
-    <row r="62" spans="1:11" ht="82.15" customHeight="1">
+    <row r="62" spans="1:11" ht="82.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="89"/>
       <c r="B62" s="41" t="s">
         <v>111</v>
@@ -9126,7 +9221,7 @@
       </c>
       <c r="K62" s="10"/>
     </row>
-    <row r="63" spans="1:11" ht="70.5" customHeight="1">
+    <row r="63" spans="1:11" ht="70.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="89"/>
       <c r="B63" s="41" t="s">
         <v>113</v>
@@ -9157,7 +9252,7 @@
       </c>
       <c r="K63" s="10"/>
     </row>
-    <row r="64" spans="1:11" ht="95.25" customHeight="1">
+    <row r="64" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="89"/>
       <c r="B64" s="42" t="s">
         <v>147</v>
@@ -9188,7 +9283,7 @@
       </c>
       <c r="K64" s="10"/>
     </row>
-    <row r="65" spans="1:11" ht="60" customHeight="1">
+    <row r="65" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="89"/>
       <c r="B65" s="42" t="s">
         <v>116</v>
@@ -9219,7 +9314,7 @@
       </c>
       <c r="K65" s="10"/>
     </row>
-    <row r="66" spans="1:11" ht="138.65" customHeight="1">
+    <row r="66" spans="1:11" ht="138.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="89"/>
       <c r="B66" s="42" t="s">
         <v>117</v>
@@ -9250,7 +9345,7 @@
       </c>
       <c r="K66" s="10"/>
     </row>
-    <row r="67" spans="1:11" ht="314.14999999999998" customHeight="1">
+    <row r="67" spans="1:11" ht="314.10000000000002" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="89"/>
       <c r="B67" s="42" t="s">
         <v>119</v>
@@ -9281,7 +9376,7 @@
       </c>
       <c r="K67" s="10"/>
     </row>
-    <row r="68" spans="1:11" ht="64.900000000000006" customHeight="1">
+    <row r="68" spans="1:11" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="89"/>
       <c r="B68" s="42" t="s">
         <v>120</v>
@@ -9309,7 +9404,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="31.5" customHeight="1">
+    <row r="69" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="89"/>
       <c r="B69" s="42" t="s">
         <v>122</v>
@@ -9337,7 +9432,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="31.5" customHeight="1">
+    <row r="70" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="89"/>
       <c r="B70" s="42" t="s">
         <v>123</v>
@@ -9367,7 +9462,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="31.5" customHeight="1">
+    <row r="71" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="89"/>
       <c r="B71" s="42" t="s">
         <v>126</v>
@@ -9397,7 +9492,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="31.5" customHeight="1">
+    <row r="72" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="89"/>
       <c r="B72" s="42" t="s">
         <v>127</v>
@@ -9427,7 +9522,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="45" customHeight="1">
+    <row r="73" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="89"/>
       <c r="B73" s="42" t="s">
         <v>135</v>
@@ -9457,7 +9552,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="28.5" customHeight="1">
+    <row r="74" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="89"/>
       <c r="B74" s="42" t="s">
         <v>169</v>
@@ -9488,7 +9583,7 @@
       </c>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:11" ht="28.5" customHeight="1">
+    <row r="75" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="89"/>
       <c r="B75" s="42" t="s">
         <v>128</v>
@@ -9519,7 +9614,7 @@
       </c>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" ht="32.25" customHeight="1">
+    <row r="76" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="89"/>
       <c r="B76" s="42" t="s">
         <v>138</v>
@@ -9549,7 +9644,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="32.25" customHeight="1">
+    <row r="77" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="89"/>
       <c r="B77" s="42" t="s">
         <v>139</v>
@@ -9579,7 +9674,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="30" customHeight="1">
+    <row r="78" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="89"/>
       <c r="B78" s="42" t="s">
         <v>141</v>
@@ -9609,7 +9704,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="42" customHeight="1">
+    <row r="79" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="49" t="s">
         <v>143</v>
       </c>
@@ -9627,8 +9722,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="9.75" customHeight="1"/>
-    <row r="81" spans="1:8">
+    <row r="80" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>162</v>
       </c>
@@ -9639,7 +9734,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>161</v>
       </c>
@@ -9647,20 +9742,20 @@
       <c r="D82" s="16"/>
       <c r="E82" s="13"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A83" s="2"/>
       <c r="B83" s="48"/>
       <c r="C83" s="17"/>
       <c r="D83" s="16"/>
       <c r="E83" s="13"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A84" s="2"/>
       <c r="C84" s="15"/>
       <c r="D84" s="16"/>
       <c r="E84" s="13"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="2"/>
       <c r="C85" s="15"/>
       <c r="D85" s="16"/>
@@ -9693,22 +9788,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="113.36328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="113.375" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.5">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>189</v>
       </c>
@@ -9716,20 +9811,20 @@
       <c r="F1" s="4"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="C2" s="3"/>
       <c r="F2" s="4"/>
       <c r="H2" s="13"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="63" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="3"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:10" ht="40.5" customHeight="1">
+    <row r="4" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="76" t="s">
         <v>0</v>
       </c>
@@ -9761,8 +9856,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+    <row r="5" spans="1:10" s="58" customFormat="1" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="91" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -9793,8 +9888,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A6" s="99"/>
+    <row r="6" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="92"/>
       <c r="B6" s="26" t="s">
         <v>16</v>
       </c>
@@ -9823,8 +9918,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A7" s="99"/>
+    <row r="7" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="92"/>
       <c r="B7" s="26" t="s">
         <v>18</v>
       </c>
@@ -9853,8 +9948,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A8" s="99"/>
+    <row r="8" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="92"/>
       <c r="B8" s="30" t="s">
         <v>21</v>
       </c>
@@ -9883,24 +9978,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A9" s="99"/>
+    <row r="9" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="92"/>
       <c r="B9" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="93" t="s">
+      <c r="C9" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="96">
         <v>5005246288</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="96">
         <v>6005126423</v>
       </c>
-      <c r="F9" s="93">
+      <c r="F9" s="96">
         <v>6005246544</v>
       </c>
-      <c r="G9" s="93" t="s">
+      <c r="G9" s="96" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="38">
@@ -9913,14 +10008,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A10" s="99"/>
+    <row r="10" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="92"/>
       <c r="B10" s="95"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
       <c r="H10" s="38">
         <v>9100</v>
       </c>
@@ -9931,8 +10026,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A11" s="99"/>
+    <row r="11" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="92"/>
       <c r="B11" s="26" t="s">
         <v>149</v>
       </c>
@@ -9961,8 +10056,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A12" s="99"/>
+    <row r="12" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="92"/>
       <c r="B12" s="26" t="s">
         <v>150</v>
       </c>
@@ -9991,8 +10086,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A13" s="99"/>
+    <row r="13" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="92"/>
       <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
@@ -10021,8 +10116,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="58" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A14" s="99"/>
+    <row r="14" spans="1:10" s="58" customFormat="1" ht="83.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="92"/>
       <c r="B14" s="42" t="s">
         <v>32</v>
       </c>
@@ -10051,8 +10146,8 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A15" s="99"/>
+    <row r="15" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="92"/>
       <c r="B15" s="42" t="s">
         <v>35</v>
       </c>
@@ -10081,8 +10176,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="58" customFormat="1" ht="84" customHeight="1">
-      <c r="A16" s="99"/>
+    <row r="16" spans="1:10" s="58" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="92"/>
       <c r="B16" s="42" t="s">
         <v>39</v>
       </c>
@@ -10111,8 +10206,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A17" s="100"/>
+    <row r="17" spans="1:10" s="58" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="93"/>
       <c r="B17" s="32" t="s">
         <v>41</v>
       </c>
@@ -10141,8 +10236,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A18" s="98" t="s">
+    <row r="18" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="91" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -10169,12 +10264,12 @@
       <c r="I18" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="92" t="s">
+      <c r="J18" s="90" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A19" s="99"/>
+    <row r="19" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="92"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
@@ -10201,8 +10296,8 @@
       </c>
       <c r="J19" s="89"/>
     </row>
-    <row r="20" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A20" s="99"/>
+    <row r="20" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="92"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
       </c>
@@ -10229,8 +10324,8 @@
       </c>
       <c r="J20" s="89"/>
     </row>
-    <row r="21" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A21" s="99"/>
+    <row r="21" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="92"/>
       <c r="B21" s="26" t="s">
         <v>53</v>
       </c>
@@ -10257,8 +10352,8 @@
       </c>
       <c r="J21" s="89"/>
     </row>
-    <row r="22" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A22" s="99"/>
+    <row r="22" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="92"/>
       <c r="B22" s="26" t="s">
         <v>55</v>
       </c>
@@ -10287,8 +10382,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A23" s="99"/>
+    <row r="23" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="92"/>
       <c r="B23" s="26" t="s">
         <v>60</v>
       </c>
@@ -10317,8 +10412,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A24" s="99"/>
+    <row r="24" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="92"/>
       <c r="B24" s="26" t="s">
         <v>195</v>
       </c>
@@ -10345,8 +10440,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A25" s="99"/>
+    <row r="25" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="92"/>
       <c r="B25" s="26" t="s">
         <v>63</v>
       </c>
@@ -10373,8 +10468,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A26" s="99"/>
+    <row r="26" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="92"/>
       <c r="B26" s="42" t="s">
         <v>197</v>
       </c>
@@ -10401,8 +10496,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A27" s="99"/>
+    <row r="27" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="92"/>
       <c r="B27" s="30" t="s">
         <v>66</v>
       </c>
@@ -10429,8 +10524,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A28" s="99"/>
+    <row r="28" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="92"/>
       <c r="B28" s="30" t="s">
         <v>68</v>
       </c>
@@ -10457,8 +10552,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A29" s="99"/>
+    <row r="29" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="92"/>
       <c r="B29" s="26" t="s">
         <v>69</v>
       </c>
@@ -10487,8 +10582,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A30" s="99"/>
+    <row r="30" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="92"/>
       <c r="B30" s="26" t="s">
         <v>72</v>
       </c>
@@ -10515,10 +10610,10 @@
       </c>
       <c r="J30" s="89"/>
     </row>
-    <row r="31" spans="1:10" s="58" customFormat="1" ht="66" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="42" t="s">
-        <v>73</v>
+    <row r="31" spans="1:10" s="58" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="92"/>
+      <c r="B31" s="102" t="s">
+        <v>216</v>
       </c>
       <c r="C31" s="43" t="s">
         <v>12</v>
@@ -10532,8 +10627,8 @@
       <c r="F31" s="43">
         <v>6005146541</v>
       </c>
-      <c r="G31" s="25" t="s">
-        <v>154</v>
+      <c r="G31" s="101" t="s">
+        <v>215</v>
       </c>
       <c r="H31" s="59">
         <v>760</v>
@@ -10545,8 +10640,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="43.5" customHeight="1">
-      <c r="A32" s="99"/>
+    <row r="32" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="92"/>
       <c r="B32" s="26" t="s">
         <v>74</v>
       </c>
@@ -10575,8 +10670,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A33" s="99"/>
+    <row r="33" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="92"/>
       <c r="B33" s="26" t="s">
         <v>77</v>
       </c>
@@ -10605,8 +10700,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A34" s="99"/>
+    <row r="34" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="92"/>
       <c r="B34" s="26" t="s">
         <v>79</v>
       </c>
@@ -10635,8 +10730,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A35" s="99"/>
+    <row r="35" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="92"/>
       <c r="B35" s="26" t="s">
         <v>80</v>
       </c>
@@ -10665,8 +10760,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A36" s="99"/>
+    <row r="36" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="92"/>
       <c r="B36" s="26" t="s">
         <v>153</v>
       </c>
@@ -10695,8 +10790,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A37" s="99"/>
+    <row r="37" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="92"/>
       <c r="B37" s="26" t="s">
         <v>82</v>
       </c>
@@ -10725,8 +10820,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A38" s="99"/>
+    <row r="38" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="92"/>
       <c r="B38" s="26" t="s">
         <v>83</v>
       </c>
@@ -10755,8 +10850,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A39" s="99"/>
+    <row r="39" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="92"/>
       <c r="B39" s="26" t="s">
         <v>84</v>
       </c>
@@ -10785,8 +10880,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A40" s="99"/>
+    <row r="40" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="92"/>
       <c r="B40" s="26" t="s">
         <v>163</v>
       </c>
@@ -10815,8 +10910,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A41" s="99"/>
+    <row r="41" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="92"/>
       <c r="B41" s="26" t="s">
         <v>85</v>
       </c>
@@ -10845,8 +10940,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A42" s="99"/>
+    <row r="42" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="92"/>
       <c r="B42" s="26" t="s">
         <v>86</v>
       </c>
@@ -10875,8 +10970,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A43" s="99"/>
+    <row r="43" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="92"/>
       <c r="B43" s="26" t="s">
         <v>88</v>
       </c>
@@ -10905,8 +11000,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A44" s="99"/>
+    <row r="44" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="92"/>
       <c r="B44" s="26" t="s">
         <v>90</v>
       </c>
@@ -10935,8 +11030,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A45" s="99"/>
+    <row r="45" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="92"/>
       <c r="B45" s="42" t="s">
         <v>168</v>
       </c>
@@ -10965,8 +11060,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="42" customHeight="1">
-      <c r="A46" s="99"/>
+    <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="92"/>
       <c r="B46" s="26" t="s">
         <v>173</v>
       </c>
@@ -10995,8 +11090,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="99.75" customHeight="1">
-      <c r="A47" s="99"/>
+    <row r="47" spans="1:10" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="92"/>
       <c r="B47" s="42" t="s">
         <v>174</v>
       </c>
@@ -11025,8 +11120,8 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="42" customHeight="1">
-      <c r="A48" s="99"/>
+    <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="92"/>
       <c r="B48" s="26" t="s">
         <v>91</v>
       </c>
@@ -11055,8 +11150,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="42" customHeight="1">
-      <c r="A49" s="99"/>
+    <row r="49" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="92"/>
       <c r="B49" s="26" t="s">
         <v>92</v>
       </c>
@@ -11085,8 +11180,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="42" customHeight="1">
-      <c r="A50" s="99"/>
+    <row r="50" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="92"/>
       <c r="B50" s="26" t="s">
         <v>94</v>
       </c>
@@ -11115,8 +11210,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A51" s="99"/>
+    <row r="51" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="92"/>
       <c r="B51" s="26" t="s">
         <v>95</v>
       </c>
@@ -11145,8 +11240,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A52" s="99"/>
+    <row r="52" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="92"/>
       <c r="B52" s="26" t="s">
         <v>96</v>
       </c>
@@ -11175,8 +11270,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A53" s="99"/>
+    <row r="53" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="92"/>
       <c r="B53" s="26" t="s">
         <v>97</v>
       </c>
@@ -11205,8 +11300,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A54" s="99"/>
+    <row r="54" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="92"/>
       <c r="B54" s="26" t="s">
         <v>99</v>
       </c>
@@ -11235,8 +11330,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="58" customFormat="1" ht="85.5" customHeight="1">
-      <c r="A55" s="99"/>
+    <row r="55" spans="1:10" s="58" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="92"/>
       <c r="B55" s="42" t="s">
         <v>101</v>
       </c>
@@ -11265,8 +11360,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A56" s="99"/>
+    <row r="56" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="92"/>
       <c r="B56" s="42" t="s">
         <v>102</v>
       </c>
@@ -11295,8 +11390,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A57" s="99"/>
+    <row r="57" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="92"/>
       <c r="B57" s="42" t="s">
         <v>104</v>
       </c>
@@ -11325,8 +11420,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A58" s="99"/>
+    <row r="58" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="92"/>
       <c r="B58" s="42" t="s">
         <v>105</v>
       </c>
@@ -11355,8 +11450,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="65" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A59" s="99"/>
+    <row r="59" spans="1:10" s="65" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="92"/>
       <c r="B59" s="56" t="s">
         <v>106</v>
       </c>
@@ -11385,8 +11480,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="71" customFormat="1" ht="60" customHeight="1">
-      <c r="A60" s="99"/>
+    <row r="60" spans="1:10" s="71" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="92"/>
       <c r="B60" s="42" t="s">
         <v>210</v>
       </c>
@@ -11415,8 +11510,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="114" customHeight="1">
-      <c r="A61" s="99"/>
+    <row r="61" spans="1:10" ht="114" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="92"/>
       <c r="B61" s="42" t="s">
         <v>107</v>
       </c>
@@ -11445,8 +11540,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="139.15" customHeight="1">
-      <c r="A62" s="99"/>
+    <row r="62" spans="1:10" ht="139.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="92"/>
       <c r="B62" s="42" t="s">
         <v>171</v>
       </c>
@@ -11475,8 +11570,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="58" customFormat="1" ht="93.75" customHeight="1">
-      <c r="A63" s="99"/>
+    <row r="63" spans="1:10" s="58" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="92"/>
       <c r="B63" s="42" t="s">
         <v>109</v>
       </c>
@@ -11505,8 +11600,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="135" customHeight="1">
-      <c r="A64" s="99"/>
+    <row r="64" spans="1:10" ht="135" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="92"/>
       <c r="B64" s="42" t="s">
         <v>110</v>
       </c>
@@ -11535,8 +11630,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="138" customHeight="1">
-      <c r="A65" s="99"/>
+    <row r="65" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="92"/>
       <c r="B65" s="41" t="s">
         <v>111</v>
       </c>
@@ -11565,8 +11660,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="96" customHeight="1">
-      <c r="A66" s="99"/>
+    <row r="66" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="92"/>
       <c r="B66" s="41" t="s">
         <v>113</v>
       </c>
@@ -11595,8 +11690,8 @@
         <v>207</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="95.25" customHeight="1">
-      <c r="A67" s="99"/>
+    <row r="67" spans="1:10" ht="95.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="92"/>
       <c r="B67" s="42" t="s">
         <v>147</v>
       </c>
@@ -11625,8 +11720,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="65" customFormat="1" ht="60" customHeight="1">
-      <c r="A68" s="99"/>
+    <row r="68" spans="1:10" s="65" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="92"/>
       <c r="B68" s="56" t="s">
         <v>116</v>
       </c>
@@ -11655,8 +11750,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="163.5" customHeight="1">
-      <c r="A69" s="99"/>
+    <row r="69" spans="1:10" ht="163.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="92"/>
       <c r="B69" s="42" t="s">
         <v>117</v>
       </c>
@@ -11685,8 +11780,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="334.5" customHeight="1">
-      <c r="A70" s="99"/>
+    <row r="70" spans="1:10" ht="334.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="92"/>
       <c r="B70" s="42" t="s">
         <v>119</v>
       </c>
@@ -11715,8 +11810,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="71" customFormat="1" ht="150" customHeight="1">
-      <c r="A71" s="100"/>
+    <row r="71" spans="1:10" s="71" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="93"/>
       <c r="B71" s="80" t="s">
         <v>211</v>
       </c>
@@ -11745,7 +11840,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="58" customFormat="1" ht="42" customHeight="1">
+    <row r="72" spans="1:10" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="49" t="s">
         <v>143</v>
       </c>
@@ -11763,10 +11858,10 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="32.25" customHeight="1">
+    <row r="73" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J73" s="79"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>162</v>
       </c>
@@ -11777,7 +11872,7 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>161</v>
       </c>
@@ -11785,38 +11880,38 @@
       <c r="D75" s="16"/>
       <c r="E75" s="13"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A76" s="2"/>
       <c r="B76" s="48"/>
       <c r="C76" s="17"/>
       <c r="D76" s="16"/>
       <c r="E76" s="13"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A77" s="2"/>
       <c r="C77" s="15"/>
       <c r="D77" s="16"/>
       <c r="E77" s="13"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A78" s="2"/>
       <c r="C78" s="15"/>
       <c r="D78" s="16"/>
       <c r="E78" s="13"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H79" s="2">
         <f>832.17/100</f>
         <v>8.3216999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H80" s="88">
         <f>H79*3</f>
         <v>24.9651</v>
       </c>
     </row>
-    <row r="81" spans="8:8">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.15">
       <c r="H81" s="2">
         <f>26500*5</f>
         <v>132500</v>
@@ -11844,17 +11939,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x010100DB24EDB465323845A68F49B67C0FBEEF" ma:contentTypeVersion="17" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="23f0dc0ab5ad78d6e6291fdb2fe26642">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3666f02-6a17-4b93-8e4f-4f8c851bed15" xmlns:ns3="a67f3886-f84f-4ade-a9df-8a61292dc710" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7e7713e468ce5fe561a860222c69c2e" ns2:_="" ns3:_="">
     <xsd:import namespace="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
@@ -12031,32 +12115,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
-    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC458EFE-CB2F-4B14-8A64-8A5C4D5C5CBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12073,4 +12143,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC0FACC-084E-4CA6-AB6A-54805DEE3D3C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BA0B11-CE17-4EF2-86D1-BF1E203BBB04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a67f3886-f84f-4ade-a9df-8a61292dc710"/>
+    <ds:schemaRef ds:uri="c3666f02-6a17-4b93-8e4f-4f8c851bed15"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>